--- a/Ontologia de Solos/Pesquisa SCOPUS/Pesquisa_Ontologia_Solos.xlsx
+++ b/Ontologia de Solos/Pesquisa SCOPUS/Pesquisa_Ontologia_Solos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\artigos\Ontologia de Solos\Pesquisa SCOPUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E421D019-437C-4B65-B9AD-85FA474BED90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F000E0-2744-44D0-97E0-FB7734E10812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="379" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8970,7 +8970,8 @@
   <dimension ref="A1:Q454"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="1" max="1" width="63.44140625" customWidth="1"/>
+    <col min="2" max="2" width="41.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
@@ -23229,5 +23230,6 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>